--- a/prompt1.xlsx
+++ b/prompt1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCBE2E9-6EF8-4497-9767-2A624541087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD7BB6C-DB6C-4743-AC15-66A199FA40BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,15 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="179">
   <si>
     <t>Sr.No.</t>
   </si>
   <si>
     <t>Sheet with data</t>
-  </si>
-  <si>
-    <t>Prompt name</t>
   </si>
   <si>
     <t>description</t>
@@ -191,33 +188,6 @@
     <t>Sr. No.</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>write consice prompts</t>
-  </si>
-  <si>
-    <t>be specific about the required information</t>
-  </si>
-  <si>
-    <t>clearly define the output format</t>
-  </si>
-  <si>
-    <t>give some example in which format output is required</t>
-  </si>
-  <si>
-    <t>write the procedure steps one by one</t>
-  </si>
-  <si>
-    <t>do not ask too much processing or information at once</t>
-  </si>
-  <si>
-    <t>if the task is complex, write simple prompts one by one and keep refining final prompt</t>
-  </si>
-  <si>
-    <t>provide the guidelines clearly to avoid the hallucination</t>
-  </si>
-  <si>
     <t>I’m going to upload an Excel file (.xlsx). 
 Please:
 1) Detect the sheets and ask me which to use (default to the first if I don’t specify).
@@ -355,7 +325,403 @@
 Proceed after I upload the Excel file; then ask me for the sheet and any required mappings.</t>
   </si>
   <si>
-    <t>demo</t>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>Tiny example</t>
+  </si>
+  <si>
+    <t>Clarity &amp; Scope</t>
+  </si>
+  <si>
+    <t>Write concise prompts</t>
+  </si>
+  <si>
+    <t>“Summarize the article in 3 bullets.”</t>
+  </si>
+  <si>
+    <t>Be specific about the required information</t>
+  </si>
+  <si>
+    <t>“List 5 risks of X, each with a 1-line mitigation.”</t>
+  </si>
+  <si>
+    <t>Define scope and exclusions</t>
+  </si>
+  <si>
+    <t>“Focus on EU law; exclude UK.”</t>
+  </si>
+  <si>
+    <t>Use clear input delimiters</t>
+  </si>
+  <si>
+    <t>“Text is between &lt;&lt;&gt;&gt; and &lt;&lt;&gt;&gt;.”</t>
+  </si>
+  <si>
+    <t>Don’t ask for too much at once</t>
+  </si>
+  <si>
+    <t>“First: outline only. Draft later.”</t>
+  </si>
+  <si>
+    <t>Structure &amp; Formatting</t>
+  </si>
+  <si>
+    <t>Clearly define the output format</t>
+  </si>
+  <si>
+    <t>Give an example of the required format</t>
+  </si>
+  <si>
+    <t>Break outputs into sections</t>
+  </si>
+  <si>
+    <t>“Sections: Summary, Risks, Next Steps.”</t>
+  </si>
+  <si>
+    <t>Write the procedure steps one by one</t>
+  </si>
+  <si>
+    <t>“1) Ingest 2) Validate 3) Export CSV.”</t>
+  </si>
+  <si>
+    <t>Specify serialization / table needs</t>
+  </si>
+  <si>
+    <t>“Output as a Markdown table.”</t>
+  </si>
+  <si>
+    <t>Process &amp; Iteration</t>
+  </si>
+  <si>
+    <t>For complex tasks, use small prompts and refine</t>
+  </si>
+  <si>
+    <t>“Draft → critique → revise.”</t>
+  </si>
+  <si>
+    <t>Use “critique then improve” loops</t>
+  </si>
+  <si>
+    <t>“Critique v1 in 5 bullets; then rewrite v2.”</t>
+  </si>
+  <si>
+    <t>Request a brief self-check before final</t>
+  </si>
+  <si>
+    <t>“Before final, list 3 checks you ran.”</t>
+  </si>
+  <si>
+    <t>Define what to do when info is missing</t>
+  </si>
+  <si>
+    <t>“If data missing, ask 2 clarifying Qs.”</t>
+  </si>
+  <si>
+    <t>Use templates with variables/slots</t>
+  </si>
+  <si>
+    <t>Reliability &amp; Safety</t>
+  </si>
+  <si>
+    <t>Provide guidelines to avoid hallucination</t>
+  </si>
+  <si>
+    <t>“If unsure, say ‘I don’t know.’”</t>
+  </si>
+  <si>
+    <t>Require citations/evidence for facts</t>
+  </si>
+  <si>
+    <t>“Cite 2 reputable sources at end.”</t>
+  </si>
+  <si>
+    <t>Define uncertainty behavior</t>
+  </si>
+  <si>
+    <t>“Flag low-confidence items with ⚠️.”</t>
+  </si>
+  <si>
+    <t>Restrict tools/data sources as needed</t>
+  </si>
+  <si>
+    <t>“Use only the attached spreadsheet.”</t>
+  </si>
+  <si>
+    <t>Provide an evaluation rubric</t>
+  </si>
+  <si>
+    <t>“Score 1–5 on clarity, accuracy, actionability.”</t>
+  </si>
+  <si>
+    <t>Style, Context &amp; Roles</t>
+  </si>
+  <si>
+    <t>Assign a role/persona/expertise level</t>
+  </si>
+  <si>
+    <t>“Act as a senior SRE.”</t>
+  </si>
+  <si>
+    <t>Specify tone and reading level</t>
+  </si>
+  <si>
+    <t>“Tone: friendly, 8th-grade reading level.”</t>
+  </si>
+  <si>
+    <t>State audience and constraints</t>
+  </si>
+  <si>
+    <t>“Audience: CFO; ≤150 words.”</t>
+  </si>
+  <si>
+    <t>Direct the creativity level</t>
+  </si>
+  <si>
+    <t>“Be conservative and literal.”</t>
+  </si>
+  <si>
+    <t>Include domain context and assumptions</t>
+  </si>
+  <si>
+    <t>“Assume 10k MAUs; SaaS B2B.”</t>
+  </si>
+  <si>
+    <t>“Return JSON: {title, steps:[]}.”</t>
+  </si>
+  <si>
+    <t>“Example: {"kpi":"CTR","target":0.12}.”</t>
+  </si>
+  <si>
+    <t>“Template: Write {n} ideas for {audience}.”</t>
+  </si>
+  <si>
+    <t>prompt objective</t>
+  </si>
+  <si>
+    <t>marketing</t>
+  </si>
+  <si>
+    <t>Create a segmented campaign for retail banking</t>
+  </si>
+  <si>
+    <t>Craft lifecycle messaging for onboarding</t>
+  </si>
+  <si>
+    <t>You are a lifecycle specialist at a bank. Create a 7-day onboarding sequence for new mobile-app users who opened a {{account type}}. Include message triggers, copy (≤120 chars for push, ≤160 for SMS), deep links, and success metrics. Add 3 personalization tokens and a fallback for missing data.</t>
+  </si>
+  <si>
+    <t>Optimize paid search keywords for loans</t>
+  </si>
+  <si>
+    <t>Act as a performance marketer. Build a keyword + negative keyword list for {{loan type}} with Indian context. Group into SKAGs, write 3 RSA headlines &amp; 2 descriptions per group, and propose bidding strategy under a CPA target of ₹{{n}}. Include extensions and compliance notes.</t>
+  </si>
+  <si>
+    <t>Build an experiment roadmap</t>
+  </si>
+  <si>
+    <t>As a marketing scientist, draft a 90-day test roadmap for cross-sell of credit cards to savings customers. Prioritize 6 experiments with hypothesis, sample size assumptions, guardrail metrics (complaints, churn), and a decision rule. Provide a simple impact vs. effort matrix.</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Define role scorecards</t>
+  </si>
+  <si>
+    <t>You are an HRBP for Corporate Banking. Create a role scorecard for “Relationship Manager—Mid-Market”. Include mission, 5–7 KPIs (leading/lagging), competencies, interview question bank, and a 30/60/90 onboarding plan. Tailor to Indian BFSI norms.</t>
+  </si>
+  <si>
+    <t>Draft a DEI recruiting prompt pack</t>
+  </si>
+  <si>
+    <t>As a recruiter, write inclusive job ad + screening prompts for “Data Analyst—Risk” avoiding biased language. Add structured interview rubric (1–5 scale), take-home exercise brief, and candidate communication templates.</t>
+  </si>
+  <si>
+    <t>Workforce planning model brief</t>
+  </si>
+  <si>
+    <t>Create a prompt that will help me generate a 12-month headcount plan for Branch Operations. Inputs: current FTE {{n}}, attrition {{%}}, productivity targets, seasonal spikes (tax season, festive). Output: monthly hiring plan, training seats, and cost forecast (INR).</t>
+  </si>
+  <si>
+    <t>Policy summarization for employees</t>
+  </si>
+  <si>
+    <t>Summarize our {{policy name, e.g., Leave &amp; Attendance}} in plain English/Hindi mix. Limit to 10 bullets, include examples, FAQs, and “what changed” vs. last version. Tone: friendly, precise, compliant.</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Draft a change request (CR)</t>
+  </si>
+  <si>
+    <t>You are an ITSM lead. Write a complete Change Request for deploying {{feature}} to the mobile app. Include scope, components, risk level, rollback plan, approvals, pre-prod tests, and implementation window aligned to IST. Present in ITIL format.</t>
+  </si>
+  <si>
+    <t>Create an incident runbook</t>
+  </si>
+  <si>
+    <t>Generate a P1 incident runbook for “Core Banking API latency &gt; {{x}} ms”. Include detection, triage steps, dashboards/queries, comms templates to business/RegTech, and a post-incident checklist (RFO, CAPA).</t>
+  </si>
+  <si>
+    <t>Vendor evaluation matrix</t>
+  </si>
+  <si>
+    <t>Prepare a comparative matrix to evaluate {{category e.g., fraud detection}} vendors. Criteria: security, RBI compliance, latency, integration effort, TCO (3 yrs), support SLAs. Request a weighted scorecard and red-flags summary.</t>
+  </si>
+  <si>
+    <t>Data retention &amp; backup prompts</t>
+  </si>
+  <si>
+    <t>Draft prompts/checklists to verify backup/restore for CBS and data lake under RBI Master Direction. Include RPO/RTO targets, test frequency, encryption, and audit artifacts to produce on demand.</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Prospecting email/call script</t>
+  </si>
+  <si>
+    <t>You are a Corporate RM. Create a 3-touch outreach (email + LinkedIn + call) for CFOs of {{industry}} firms with ₹{{revenue}} revenue to pitch {{product}}. Include objection handling, meeting ask, and compliance-safe benefits.</t>
+  </si>
+  <si>
+    <t>Account plan template</t>
+  </si>
+  <si>
+    <t>Build a 1-page account plan for a top-100 client. Sections: org map, wallet sizing, share of wallet, competitor footprint, cross-sell plays, 3-month action plan, risk signals, and next best product. Output as a fillable outline.</t>
+  </si>
+  <si>
+    <t>Branch sales huddle guide</t>
+  </si>
+  <si>
+    <t>Write a daily 15-minute branch huddle script to boost {{metric, e.g., CASA}}. Include yesterday’s numbers, micro-training, today’s 3 tasks, and a quick role-play. Provide a whiteboard template.</t>
+  </si>
+  <si>
+    <t>Proposal generator</t>
+  </si>
+  <si>
+    <t>Draft a proposal for a {{loan/treasury}} deal to {{client name, anonymized}}. Include exec summary, pricing table, covenants, risk disclosures, and onboarding checklist. Output: doc outline + editable tables.</t>
+  </si>
+  <si>
+    <t>employee training</t>
+  </si>
+  <si>
+    <t>Micro-learning module</t>
+  </si>
+  <si>
+    <t>Design a 10-minute micro-learning on “KYC &amp; AML red flags for frontline staff”. Provide learning objectives, 6 slide titles with speaker notes, 5-question quiz (with answers), and 2 scenario role-plays.</t>
+  </si>
+  <si>
+    <t>Simulation prompt</t>
+  </si>
+  <si>
+    <t>Create a branching dialogue simulation for handling a customer disputing a card charge. Include customer persona, 4 branches, compliance guardrails, and scoring rubric.</t>
+  </si>
+  <si>
+    <t>Product knowledge flashcards</t>
+  </si>
+  <si>
+    <t>Generate 20 flashcards (Q/A) for {{product e.g., overdraft protection}}. Mix definition, scenario, numbers, and compliance questions. Provide CSV columns: front, back, tag.</t>
+  </si>
+  <si>
+    <t>Supervisor coaching guide</t>
+  </si>
+  <si>
+    <t>Write a 30-day coaching plan to improve teller cross-sell. Include weekly goals, observation checklist, sample feedback scripts (SBI: Situation-Behavior-Impact), and measurement plan.</t>
+  </si>
+  <si>
+    <t>coding</t>
+  </si>
+  <si>
+    <t>API spec to code stub</t>
+  </si>
+  <si>
+    <t>Data quality validators</t>
+  </si>
+  <si>
+    <t>Generate Great Expectations tests for a transactions table with columns {{list}}. Include checks for nulls, ranges, referential integrity, and anomaly detection. Provide YAML + Python example.</t>
+  </si>
+  <si>
+    <t>Secure secrets management</t>
+  </si>
+  <si>
+    <t>Provide a Terraform + Kubernetes manifest setup to store service secrets in {{Vault/KMS}} with rotation every {{n}} days. Include RBAC, audit logging, and a runbook to rotate keys safely.</t>
+  </si>
+  <si>
+    <t>Performance profiling prompt</t>
+  </si>
+  <si>
+    <t>machine learning codes (data processing)</t>
+  </si>
+  <si>
+    <t>Build a feature pipeline</t>
+  </si>
+  <si>
+    <t>Write Python (PySpark or Pandas) to ingest transactions, clean, and engineer features for credit-risk modeling: rolling spend, salary detection, delinquency flags, bureau merges. Include unit tests and data dictionaries.</t>
+  </si>
+  <si>
+    <t>machine learning codes (modelling)</t>
+  </si>
+  <si>
+    <t>Train a default model</t>
+  </si>
+  <si>
+    <t>Produce code to train and compare Logistic Regression, XGBoost, and LightGBM for 90-day default prediction. Include stratified CV, class imbalance handling, SHAP importance, and model registry logging. Provide a CLI entry point.</t>
+  </si>
+  <si>
+    <t>machine learning codes (evaluation)</t>
+  </si>
+  <si>
+    <t>Robust evaluation &amp; fairness</t>
+  </si>
+  <si>
+    <t>Generate a notebook section that computes AUC, KS, PR-AUC, calibration plots, and fairness metrics across age/region segments. Include backtesting by vintage month and a decision threshold finder optimizing F1 under a bad-rate cap.</t>
+  </si>
+  <si>
+    <t>machine learning codes (MLOps)</t>
+  </si>
+  <si>
+    <t>Deployment &amp; monitoring</t>
+  </si>
+  <si>
+    <t>Create code + config to deploy the best model as a REST endpoint (FastAPI) with pydantic schema, drift monitoring (evidently), canary release, and monthly performance reports auto-emailed.</t>
+  </si>
+  <si>
+    <t>business users/executives</t>
+  </si>
+  <si>
+    <t>Board-ready metric brief</t>
+  </si>
+  <si>
+    <t>Draft a 1-page brief for the CEO on Q{{n}} Retail Banking performance. Sections: growth, margins, risk (NPA/NNPA), CX (NPS), digital adoption, compliance. Include 5 charts to request from BI and 3 key decisions needed.</t>
+  </si>
+  <si>
+    <t>Strategy options memo</t>
+  </si>
+  <si>
+    <t>Prepare a “3 strategic options” memo to grow SME lending by {{x}}% in 12 months. For each option: thesis, investments, risk, regulatory considerations, and “how to test in 90 days”. End with a clear recommendation.</t>
+  </si>
+  <si>
+    <t>Pricing decision support</t>
+  </si>
+  <si>
+    <t>Build a prompt to analyze pricing for a new {{product}}. Inputs: cost of funds {{%}}, benchmark rates, competitor pricing, target ROA {{%}}. Output: recommended price band, sensitivity table, and guardrails to avoid adverse selection.</t>
+  </si>
+  <si>
+    <t>Risk appetite statement</t>
+  </si>
+  <si>
+    <t>Create a concise Risk Appetite Statement for Retail Assets. Define tolerances for credit, market, liquidity, operational risks with 5–7 quantitative limits (e.g., PD, LGD, LCR) and an escalation protocol. Include a dashboard spec.</t>
+  </si>
+  <si>
+    <t>Role: Senior Bank Marketer. Goal: Design a cross-channel campaign to increase uptake of {{product e.g., high-yield savings}} among {{segment e.g., salaried millennials in Tier-1 cities}}. Inputs: Current CTR {{x%}}, CVR {{y%}}, CAC ceiling ₹{{n}}. Constraints: RBI advertising guidelines; no misrepresentation of returns. Deliverables: 3 audience personas, value props, channel mix (email/SMS/in-app/paid), sample creatives (subject lines + copy), KPI targets and test plan (A/B matrices). Output: A 1-page plan + a 2-week rollout calendar.</t>
+  </si>
+  <si>
+    <t>Convert this OpenAPI snippet to production-ready Python FastAPI stubs with Pydantic models, auth middleware (JWT), rate limiting, and unit tests: {{OpenAPI JSON}}. Include folder structure and Makefile tasks.</t>
+  </si>
+  <si>
+    <t>Given this Python code block, produce a profiling report (cProfile) and optimized version achieving ≥{{x}}% speedup. Explain trade-offs and add tests to ensure parity. Code: {{code}}</t>
   </si>
 </sst>
 </file>
@@ -391,7 +757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -414,11 +780,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -427,8 +830,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:G48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -728,16 +1146,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.35">
@@ -745,19 +1163,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
@@ -766,16 +1184,16 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
@@ -783,19 +1201,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -803,19 +1221,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
@@ -823,19 +1241,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
@@ -843,19 +1261,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
@@ -864,14 +1282,14 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -880,14 +1298,14 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
@@ -896,14 +1314,14 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
@@ -912,14 +1330,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
@@ -928,14 +1346,14 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
@@ -944,14 +1362,14 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.35">
@@ -960,14 +1378,14 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
@@ -976,14 +1394,14 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
@@ -992,14 +1410,510 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>56</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="2">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="2">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="2">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="2">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="2">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="2">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="2">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="2">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="2">
+        <v>24</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="2">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="2">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="2">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="2">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="2">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="2">
+        <v>30</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="2">
+        <v>31</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B34" s="2">
+        <v>32</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="2">
+        <v>33</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="2">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="2">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="2">
+        <v>36</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="2">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="2">
+        <v>38</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="2">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="2">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B43" s="2">
+        <v>41</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="2">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="2">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="2">
+        <v>44</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B47" s="2">
+        <v>45</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B48" s="2">
+        <v>46</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1009,85 +1923,347 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C4B642-5FFB-42FB-B1C4-848301C64E26}">
-  <dimension ref="B2:C10"/>
+  <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C4" s="5"/>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="C5" s="5"/>
+      <c r="D5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C6" s="5"/>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="C7" s="6"/>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="C9" s="5"/>
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
+      <c r="C10" s="5"/>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B16" s="2">
+        <v>14</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="2">
+        <v>15</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" s="2">
+        <v>16</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" s="2">
+        <v>17</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="2">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" s="2">
+        <v>19</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" s="2">
+        <v>20</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B23" s="2">
+        <v>21</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="2">
+        <v>22</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B25" s="2">
+        <v>23</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B26" s="2">
+        <v>24</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B27" s="2">
+        <v>25</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prompt1.xlsx
+++ b/prompt1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD7BB6C-DB6C-4743-AC15-66A199FA40BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E608F01-AA11-4286-8583-238E20CAEBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prompt dictionary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="248">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -722,6 +722,213 @@
   </si>
   <si>
     <t>Given this Python code block, produce a profiling report (cProfile) and optimized version achieving ≥{{x}}% speedup. Explain trade-offs and add tests to ensure parity. Code: {{code}}</t>
+  </si>
+  <si>
+    <t>serial number</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Create a customer segmentation campaign brief for retail banking</t>
+  </si>
+  <si>
+    <t>Generate compliant email copy variants for an offer</t>
+  </si>
+  <si>
+    <t>Build a media mix and budget plan</t>
+  </si>
+  <si>
+    <t>Create a journey map for mortgage acquisition</t>
+  </si>
+  <si>
+    <t>Draft a role JD for a bank data analyst</t>
+  </si>
+  <si>
+    <t>Design a performance review rubric for branch staff</t>
+  </si>
+  <si>
+    <t>Create onboarding plan for risk/analytics hires</t>
+  </si>
+  <si>
+    <t>Draft internal comms for policy update</t>
+  </si>
+  <si>
+    <t>Create incident runbook for core banking outage</t>
+  </si>
+  <si>
+    <t>Define access control policy for analytics data</t>
+  </si>
+  <si>
+    <t>Draft API standards for internal services</t>
+  </si>
+  <si>
+    <t>Create backlog for mobile app security hardening</t>
+  </si>
+  <si>
+    <t>Build a prospecting script for SME loans</t>
+  </si>
+  <si>
+    <t>Construct an account plan for a corporate client</t>
+  </si>
+  <si>
+    <t>Prepare proposal for treasury services</t>
+  </si>
+  <si>
+    <t>Create KPI dashboard spec for RM team</t>
+  </si>
+  <si>
+    <t>Create micro-learning on AML red flags</t>
+  </si>
+  <si>
+    <t>Build simulation for loan underwriting</t>
+  </si>
+  <si>
+    <t>Draft SOP checklist training for account opening</t>
+  </si>
+  <si>
+    <t>Design phishing awareness campaign</t>
+  </si>
+  <si>
+    <t>coding (EDA, SAS→Python, data processing)</t>
+  </si>
+  <si>
+    <t>Produce EDA notebook plan for retail transactions</t>
+  </si>
+  <si>
+    <t>Translate SAS data step to idiomatic pandas</t>
+  </si>
+  <si>
+    <t>Build robust data filtering/joins pipeline</t>
+  </si>
+  <si>
+    <t>Create a reusable data quality report</t>
+  </si>
+  <si>
+    <t>machine learning codes (preprocessing→evaluation)</t>
+  </si>
+  <si>
+    <t>Full ML pipeline for credit default</t>
+  </si>
+  <si>
+    <t>Feature engineering for transactions</t>
+  </si>
+  <si>
+    <t>Model monitoring and drift detection</t>
+  </si>
+  <si>
+    <t>Explainability &amp; fairness checks</t>
+  </si>
+  <si>
+    <t>business users / executives</t>
+  </si>
+  <si>
+    <t>Executive brief on deposit outflows</t>
+  </si>
+  <si>
+    <t>Board pack slide outline for risk update</t>
+  </si>
+  <si>
+    <t>Product P&amp;L and pricing sensitivity</t>
+  </si>
+  <si>
+    <t>Regulatory change impact memo</t>
+  </si>
+  <si>
+    <t>Role: You are a senior bank marketer. Task: Draft a campaign brief to target high-value retail customers for {{product_type e.g., savings+, credit card, personal loan}}. Data available: {{key insights}}. Constraints: Comply with {{regulation list e.g., RBI/GLBA}}, avoid discriminatory targeting, ensure opt-out language. Deliverables: (1) ICP definition, (2) value prop, (3) offer &amp; eligibility rules, (4) channels &amp; cadence, (5) KPIs with targets, (6) risks &amp; mitigations. Output: Structured markdown with bullets and a timeline (Gantt-style list).</t>
+  </si>
+  <si>
+    <t>Role: Direct response copywriter for a bank. Objective: Create 5 subject lines and 3 body copy variants to promote {{offer}} to {{segment}}. Tone: Trustworthy, clear, benefit-led. Compliance: No misleading APRs; include required disclaimers: {{disclaimer text}}. Constraints: ≤45-char subject lines; landing page CTA: {{CTA}}. Output: Table with columns: Version, Subject, Preview Text, Body (&lt;=120 words), CTA, Disclaimer.</t>
+  </si>
+  <si>
+    <t>Context: Budget ₹{{X}} for {{quarter}} to drive {{goal e.g., new accounts}}. Task: Propose a channel mix (Search, Social, Programmatic, Branch, Email, Affiliates). Include: spend %, CPM/CPC assumptions, expected reach, leads, CPA, and sensitivity (±20% CPC). Constraints: Target {{geo/age}}, exclude {{sensitive groups}}. Output: A table + bullet rationale; show formulas used.</t>
+  </si>
+  <si>
+    <t>Role: CX strategist. Goal: Map end-to-end journey for {{mortgage type}} from awareness→onboarding. Include: stages, customer goals, bank actions, comms, data captured, compliance checks (KYC, consent), drop-off risks, and recovery tactics. Output: Markdown table + top 5 improvements ranked by impact/effort.</t>
+  </si>
+  <si>
+    <t>Role: HRBP at a bank. Task: Write a job description for “Data Analyst – Retail Banking”. Include: mission, day-to-day, required/desired skills, KPIs within 6 months, tech stack, location, pay band range, EEO statement, background check note. Output: Clean JD plus interview scorecard with criteria &amp; weights.</t>
+  </si>
+  <si>
+    <t>Objective: Build a quarterly review rubric for {{role e.g., Relationship Manager}}. Dimensions: sales, compliance adherence, CSAT/NPS, error rate, learning credits. Scoring: 1–5 with behavioral anchors. Output: Table rubric + calibration guidance + improvement plan template.</t>
+  </si>
+  <si>
+    <t>Task: 30-60-90 day plan for {{position}} in Risk/Analytics. Include: systems access, mandatory trainings (AML/KYC, data privacy), success metrics, shadowing plan, first project scope. Output: Timeline table + checklist.</t>
+  </si>
+  <si>
+    <t>Context: Update to {{leave/remote work/expense}} policy. Task: Write all-hands email + FAQ for managers. Constraints: Clear, inclusive, link to policy doc, effective date {{date}}. Output: Email (≤250 words) + 8-10 FAQs.</t>
+  </si>
+  <si>
+    <t>Role: ITSM lead. Scenario: Core banking API latency &gt; {{threshold}} for {{duration}}. Task: Draft L1→L3 runbook: detection, triage, rollback, comms templates (internal/external), SLAs, post-incident review template. Output: Step list + decision tree + status page snippet.</t>
+  </si>
+  <si>
+    <t>Objective: Propose RBAC for data warehouse (PII, PCI, non-PII). Constraints: Least privilege, data masking, audit logging, break-glass protocol. Include: roles, permissions, example queries blocked/allowed, approval workflow. Output: Policy doc + table mapping roles→datasets.</t>
+  </si>
+  <si>
+    <t>Task: Write REST standards for banking microservices. Include: versioning, auth (OAuth2/JWT), idempotency, error codes, rate limits, observability, PII handling. Output: Markdown spec with request/response examples.</t>
+  </si>
+  <si>
+    <t>Context: Next quarter security sprint. Task: Prioritize backlog items (CWE, OWASP MASVS), estimate effort, acceptance criteria, and risk reduction score. Output: Backlog table (rank, item, rationale, effort, risk↓).</t>
+  </si>
+  <si>
+    <t>Role: Relationship Manager. Task: Cold-call and email scripts for SMEs in {{industry}} seeking ₹{{loan size}}. Include: discovery questions, objection handling, required docs, cross-sell cues (cash mgmt, POS), compliance phrasing. Output: Call flow + 2 email templates.</t>
+  </si>
+  <si>
+    <t>Objective: 12-month plan for {{client}}. Include: org map, needs analysis, solution stack (transaction banking, FX, credit), competitive risks, whitespace, quarterly targets, exec sponsor asks. Output: One-pager + metrics table.</t>
+  </si>
+  <si>
+    <t>Task: Draft proposal to win {{RFP name}}. Constraints: Detail SLAs, onboarding, pricing, service credits, references, and info security posture. Output: Structured proposal with exec summary + annexures.</t>
+  </si>
+  <si>
+    <t>Goal: Define dashboard requirements. Metrics: pipeline, win rate, average deal cycle, product mix, cross-sell ratio, churn. Data sources: {{CRM, core}}, refresh cadence, access levels. Output: Wireframe description + metric definitions table.</t>
+  </si>
+  <si>
+    <t>Role: L&amp;D specialist. Task: Build a 10-minute module on AML/KYC red flags for frontline staff. Include: objectives, 6 scenarios, quiz (6 Qs), answer key, references. Output: Lesson plan + quiz items.</t>
+  </si>
+  <si>
+    <t>Objective: Case-based exercise on underwriting a {{loan type}}. Provide: dataset schema outline, decision checkpoints, scoring rubric, sample solution narrative. Constraints: Stress fair lending &amp; documentation. Output: Instructor + learner guides.</t>
+  </si>
+  <si>
+    <t>Task: Step-by-step SOP with screenshots placeholders, compliance checks, error traps, escalation path, time targets per step. Output: Checklist + RACI.</t>
+  </si>
+  <si>
+    <t>Goal: Reduce click-through by {{target}}. Deliverables: 3 email templates (benign), landing copy, reporting instructions, metrics plan, comms cadence. Output: Campaign doc with timeline.</t>
+  </si>
+  <si>
+    <t>Input: Transaction table schema {{columns}} + target {{fraud_flag/attrition}}. Task: Outline EDA steps and write Python code cells (pandas, matplotlib only) to load, profile (types, missingness), univariate, bivariate, leakage checks, and save a profiling report. Output: Code blocks with comments and a final summary cell.</t>
+  </si>
+  <si>
+    <t>Input: SAS code:\nsas\n{{SAS_CODE}}\n\nTask: Translate into idiomatic Python (pandas) preserving logic (BY groups, retain, formats, merges). Also: Call out any semantic mismatches, propose tests, and show before/after example with small DataFrame. Output: Python code + notes.</t>
+  </si>
+  <si>
+    <t>Context: Datasets: customers, accounts, transactions. Task: Write Python code to de-duplicate, standardize IDs, join with anti-join logic, filter to active accounts, and flag anomalies (negative balances, date gaps). Constraints: Large data → use chunking/polars option. Output: Well-commented code + complexity notes.</t>
+  </si>
+  <si>
+    <t>Task: Implement a function dq_report(df, rules) to validate rules (uniqueness, ranges, regex, cross-field). Output: Python code returning a tidy DataFrame of failures with row ids, rule, column, value, and severity, plus an example on {{dataset}}.</t>
+  </si>
+  <si>
+    <t>Data: {{features list}}; target: default_flag. Task: Write Python (scikit-learn) to: split (time-aware), impute, encode, scale, handle class imbalance, feature selection, train {{models e.g., Logistic, XGBoost}}, cross-validate, calibrate probabilities, evaluate (AUC, KS, PR-AUC), and export artifacts. Output: Single script with CLI args and clear sections.</t>
+  </si>
+  <si>
+    <t>Objective: Create customer-level features from transactions (RFM, velocity, merchant entropy, rolling stats, delinquency markers). Constraints: leakage-safe windows. Output: Python functions with docstrings + unit tests (pytest style).</t>
+  </si>
+  <si>
+    <t>Task: Code to log prediction distributions, PSI/JS divergence, data drift (KS/AD), performance by cohort, alert thresholds. Output: A monitor.py module + example usage with synthetic data.</t>
+  </si>
+  <si>
+    <t>Goal: Post-hoc explain {{model}} with SHAP/Permutation, produce cohort fairness metrics (SPD, EOD) for protected proxies {{list}}. Output: Notebook cells + narrative on limitations and mitigations.</t>
+  </si>
+  <si>
+    <t>Role: Strategy lead. Task: Summarize drivers of deposit outflows for {{segment/region}} in {{period}}. Include: data snapshot, top 5 drivers, competitive moves, rate sensitivity bands, operational risks, recommended actions with ROI and risk notes. Output: One-pager with bullets + chart spec.</t>
+  </si>
+  <si>
+    <t>Objective: Outline 5 slides for Board Risk Committee: credit, market, liquidity, operational (incl. cyber), conduct. Include: 3 key metrics/slide, status lights, trend since {{Q-1}}, and decisions required. Output: Slide outline + appendix list.</t>
+  </si>
+  <si>
+    <t>Task: Build a pricing sensitivity narrative for {{product}}. Provide: base P&amp;L table, elasticity assumptions, scenarios (−50bps to +50bps), impact on volume, NIM, CAC, churn. Output: Summary + recommendation and risks.</t>
+  </si>
+  <si>
+    <t>Context: New regulation {{name}} effective {{date}}. Task: Write a two-page memo: scope, impacted processes, cost estimate, tech changes, training needs, timeline, and go/no-go checkpoints. Output: Executive memo with clear owner &amp; RAIDs.</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G48"/>
+  <dimension ref="B2:G83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -1914,6 +2121,468 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" t="s">
+        <v>182</v>
+      </c>
+      <c r="E53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>183</v>
+      </c>
+      <c r="E54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" t="s">
+        <v>184</v>
+      </c>
+      <c r="E55" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>185</v>
+      </c>
+      <c r="E56" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>186</v>
+      </c>
+      <c r="E57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
+        <v>187</v>
+      </c>
+      <c r="E58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B60">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>121</v>
+      </c>
+      <c r="D60" t="s">
+        <v>189</v>
+      </c>
+      <c r="E60" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B61">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E61" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>121</v>
+      </c>
+      <c r="D62" t="s">
+        <v>191</v>
+      </c>
+      <c r="E62" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B63">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" t="s">
+        <v>192</v>
+      </c>
+      <c r="E63" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B64">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" t="s">
+        <v>193</v>
+      </c>
+      <c r="E64" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B65">
+        <v>14</v>
+      </c>
+      <c r="C65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" t="s">
+        <v>194</v>
+      </c>
+      <c r="E65" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B66">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B67">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B68">
+        <v>17</v>
+      </c>
+      <c r="C68" t="s">
+        <v>139</v>
+      </c>
+      <c r="D68" t="s">
+        <v>197</v>
+      </c>
+      <c r="E68" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B69">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>139</v>
+      </c>
+      <c r="D69" t="s">
+        <v>198</v>
+      </c>
+      <c r="E69" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B70">
+        <v>19</v>
+      </c>
+      <c r="C70" t="s">
+        <v>139</v>
+      </c>
+      <c r="D70" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B71">
+        <v>20</v>
+      </c>
+      <c r="C71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" t="s">
+        <v>200</v>
+      </c>
+      <c r="E71" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B72">
+        <v>21</v>
+      </c>
+      <c r="C72" t="s">
+        <v>201</v>
+      </c>
+      <c r="D72" t="s">
+        <v>202</v>
+      </c>
+      <c r="E72" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B73">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>201</v>
+      </c>
+      <c r="D73" t="s">
+        <v>203</v>
+      </c>
+      <c r="E73" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B74">
+        <v>23</v>
+      </c>
+      <c r="C74" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" t="s">
+        <v>204</v>
+      </c>
+      <c r="E74" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B75">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" t="s">
+        <v>205</v>
+      </c>
+      <c r="E75" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B76">
+        <v>25</v>
+      </c>
+      <c r="C76" t="s">
+        <v>206</v>
+      </c>
+      <c r="D76" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B77">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D77" t="s">
+        <v>208</v>
+      </c>
+      <c r="E77" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B78">
+        <v>27</v>
+      </c>
+      <c r="C78" t="s">
+        <v>206</v>
+      </c>
+      <c r="D78" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B79">
+        <v>28</v>
+      </c>
+      <c r="C79" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B80">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>211</v>
+      </c>
+      <c r="D80" t="s">
+        <v>212</v>
+      </c>
+      <c r="E80" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B81">
+        <v>30</v>
+      </c>
+      <c r="C81" t="s">
+        <v>211</v>
+      </c>
+      <c r="D81" t="s">
+        <v>213</v>
+      </c>
+      <c r="E81" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B82">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>211</v>
+      </c>
+      <c r="D82" t="s">
+        <v>214</v>
+      </c>
+      <c r="E82" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B83">
+        <v>32</v>
+      </c>
+      <c r="C83" t="s">
+        <v>211</v>
+      </c>
+      <c r="D83" t="s">
+        <v>215</v>
+      </c>
+      <c r="E83" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/prompt1.xlsx
+++ b/prompt1.xlsx
@@ -8,15 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E608F01-AA11-4286-8583-238E20CAEBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEF61A4-7E89-4CBA-B69A-4C7114C02145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prompt dictionary" sheetId="1" r:id="rId1"/>
     <sheet name="prompt best practices" sheetId="2" r:id="rId2"/>
+    <sheet name="NW HYSA" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NW HYSA'!$C$4:$E$118</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="273">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -930,12 +937,103 @@
   <si>
     <t>Context: New regulation {{name}} effective {{date}}. Task: Write a two-page memo: scope, impacted processes, cost estimate, tech changes, training needs, timeline, and go/no-go checkpoints. Output: Executive memo with clear owner &amp; RAIDs.</t>
   </si>
+  <si>
+    <t xml:space="preserve">Prompt --&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit the following page 
+https://www.nerdwallet.com/best/banking/high-yield-online-savings-accounts 
+scrap all the content which is available on the page.
+extract the data under heading ```Best High-Yield Savings Accounts of {current month} 2025: ```
+provide the data in a tabular format 
+Rank (1, 2, 3, …)
+Bank/Institution name (short name)
+Product name (full name with bank)
+APY (annual percentage yield)
+rating
+Bonus: if any (empty if not available)
+Notes: (minimum balance, eligibility, account type, restrictions — if not stated, empty)
+</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Bank / Institution</t>
+  </si>
+  <si>
+    <t>American Express</t>
+  </si>
+  <si>
+    <t>Daily Rank</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Axos Bank</t>
+  </si>
+  <si>
+    <t>Barclays</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>CIT Bank</t>
+  </si>
+  <si>
+    <t>Discover</t>
+  </si>
+  <si>
+    <t>E*TRADE (Morgan Stanley)</t>
+  </si>
+  <si>
+    <t>EverBank</t>
+  </si>
+  <si>
+    <t>Marcus (Goldman Sachs)</t>
+  </si>
+  <si>
+    <t>Openbank</t>
+  </si>
+  <si>
+    <t>SoFi</t>
+  </si>
+  <si>
+    <t>Synchrony Bank</t>
+  </si>
+  <si>
+    <t>UFB Direct</t>
+  </si>
+  <si>
+    <t>Western Alliance (via Raisin)</t>
+  </si>
+  <si>
+    <t>Forbright Bank</t>
+  </si>
+  <si>
+    <t>LendingClub</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -949,8 +1047,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -960,6 +1063,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,7 +1137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1055,6 +1164,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,6 +1191,6931 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[prompt1.xlsx]NW HYSA!PivotTable2</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="24"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="25"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="26"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="27"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="28"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="29"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="31"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="32"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="33"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="34"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="35"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$K$7:$K$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>American Express</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$K$9:$K$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$L$7:$L$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Axos Bank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$L$9:$L$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$M$7:$M$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Barclays</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$M$9:$M$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$N$7:$N$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Capital One</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$N$9:$N$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$O$7:$O$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CIT Bank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$O$9:$O$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$P$7:$P$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Discover</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$P$9:$P$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$Q$7:$Q$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E*TRADE (Morgan Stanley)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$Q$9:$Q$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$R$7:$R$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EverBank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$R$9:$R$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$S$7:$S$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Marcus (Goldman Sachs)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$S$9:$S$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$T$7:$T$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Openbank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$T$9:$T$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$U$7:$U$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SoFi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$U$9:$U$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$V$7:$V$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Synchrony Bank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$V$9:$V$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$W$7:$W$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>UFB Direct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$W$9:$W$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$X$7:$X$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Western Alliance (via Raisin)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$X$9:$X$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$Y$7:$Y$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Forbright Bank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$Y$9:$Y$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'NW HYSA'!$Z$7:$Z$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LendingClub</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'NW HYSA'!$J$9:$J$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>08 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>09 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31 October 2025</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>03 November 2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'NW HYSA'!$Z$9:$Z$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-402D-4526-828F-ECB5A2AB0266}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="186129824"/>
+        <c:axId val="186123104"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="186129824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="186123104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="186123104"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="186129824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8381895C-B009-43B0-BE8F-4A09FB6D06BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mohit Verma" refreshedDate="45964.706322453705" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="156" xr:uid="{1B03C5B9-65BD-4DD2-A477-9377FED367DA}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="C4:E160" sheet="NW HYSA" r:id="rId2"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-10-08T00:00:00" maxDate="2025-11-04T00:00:00" count="12">
+        <d v="2025-10-08T00:00:00"/>
+        <d v="2025-10-09T00:00:00"/>
+        <d v="2025-10-10T00:00:00"/>
+        <d v="2025-10-13T00:00:00"/>
+        <d v="2025-10-14T00:00:00"/>
+        <d v="2025-10-15T00:00:00"/>
+        <d v="2025-10-16T00:00:00"/>
+        <d v="2025-11-03T00:00:00"/>
+        <d v="2025-10-28T00:00:00"/>
+        <d v="2025-10-29T00:00:00"/>
+        <d v="2025-10-30T00:00:00"/>
+        <d v="2025-10-31T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Rank" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="16"/>
+    </cacheField>
+    <cacheField name="Bank / Institution" numFmtId="0">
+      <sharedItems count="16">
+        <s v="American Express"/>
+        <s v="Axos Bank"/>
+        <s v="Barclays"/>
+        <s v="Capital One"/>
+        <s v="CIT Bank"/>
+        <s v="Discover"/>
+        <s v="E*TRADE (Morgan Stanley)"/>
+        <s v="EverBank"/>
+        <s v="Forbright Bank"/>
+        <s v="LendingClub"/>
+        <s v="Marcus (Goldman Sachs)"/>
+        <s v="Openbank"/>
+        <s v="SoFi"/>
+        <s v="Synchrony Bank"/>
+        <s v="UFB Direct"/>
+        <s v="Western Alliance (via Raisin)"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="156">
+  <r>
+    <x v="0"/>
+    <n v="7"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="7"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="8"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="8"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="9"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="8"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="8"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="9"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="11"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="11"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="12"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="12"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="13"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="11"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="11"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="9"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="9"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="10"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="11"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="10"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="10"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="9"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="9"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="8"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="7"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="7"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="5"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="5"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="6"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="6"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="6"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="5"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="5"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="5"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="12"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="12"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="13"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="11"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="10"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="10"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="11"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="14"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="14"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="16"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="15"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="15"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="14"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="11"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="4"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="4"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="4"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="15"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="14"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="3"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="13"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="5"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="6"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="7"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="7"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="7"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="6"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="6"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="5"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="5"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="11"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="11"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="12"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="12"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="12"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="7"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="7"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="6"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="8"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="8"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="6"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="8"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="8"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="8"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="9"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="9"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="10"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="9"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="9"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="8"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="7"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="6"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="13"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="13"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="13"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="14"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="14"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="13"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="9"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="9"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="6"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="6"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="7"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="7"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="8"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="5"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="5"/>
+    <x v="15"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="J7:AA21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="17">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Daily Rank" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="32">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="27" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="28" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="29" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="30" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="31" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="32" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="33" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="34" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="35" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2935,4 +9981,2444 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD380F4D-AC9C-4F9E-8708-F19AE0363608}">
+  <dimension ref="C2:AA160"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:27" ht="29" x14ac:dyDescent="0.35">
+      <c r="C2" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C4" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C5" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D5" s="2">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C6" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D6" s="2">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C7" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="J7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C8" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D8" s="2">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="J8" t="s">
+        <v>256</v>
+      </c>
+      <c r="K8" t="s">
+        <v>253</v>
+      </c>
+      <c r="L8" t="s">
+        <v>257</v>
+      </c>
+      <c r="M8" t="s">
+        <v>258</v>
+      </c>
+      <c r="N8" t="s">
+        <v>259</v>
+      </c>
+      <c r="O8" t="s">
+        <v>260</v>
+      </c>
+      <c r="P8" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>262</v>
+      </c>
+      <c r="R8" t="s">
+        <v>263</v>
+      </c>
+      <c r="S8" t="s">
+        <v>264</v>
+      </c>
+      <c r="T8" t="s">
+        <v>265</v>
+      </c>
+      <c r="U8" t="s">
+        <v>266</v>
+      </c>
+      <c r="V8" t="s">
+        <v>267</v>
+      </c>
+      <c r="W8" t="s">
+        <v>268</v>
+      </c>
+      <c r="X8" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C9" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D9" s="2">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="J9" s="15">
+        <v>45938</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>11</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="P9">
+        <v>12</v>
+      </c>
+      <c r="Q9">
+        <v>14</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>5</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>10</v>
+      </c>
+      <c r="V9">
+        <v>8</v>
+      </c>
+      <c r="W9">
+        <v>13</v>
+      </c>
+      <c r="X9">
+        <v>6</v>
+      </c>
+      <c r="AA9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C10" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D10" s="2">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="J10" s="15">
+        <v>45939</v>
+      </c>
+      <c r="K10">
+        <v>7</v>
+      </c>
+      <c r="L10">
+        <v>11</v>
+      </c>
+      <c r="M10">
+        <v>9</v>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <v>12</v>
+      </c>
+      <c r="Q10">
+        <v>14</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>5</v>
+      </c>
+      <c r="T10">
+        <v>2</v>
+      </c>
+      <c r="U10">
+        <v>10</v>
+      </c>
+      <c r="V10">
+        <v>8</v>
+      </c>
+      <c r="W10">
+        <v>13</v>
+      </c>
+      <c r="X10">
+        <v>6</v>
+      </c>
+      <c r="AA10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C11" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D11" s="2">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="J11" s="15">
+        <v>45940</v>
+      </c>
+      <c r="K11">
+        <v>8</v>
+      </c>
+      <c r="L11">
+        <v>12</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
+        <v>13</v>
+      </c>
+      <c r="Q11">
+        <v>16</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>6</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>11</v>
+      </c>
+      <c r="V11">
+        <v>9</v>
+      </c>
+      <c r="W11">
+        <v>14</v>
+      </c>
+      <c r="X11">
+        <v>7</v>
+      </c>
+      <c r="Y11">
+        <v>3</v>
+      </c>
+      <c r="Z11">
+        <v>15</v>
+      </c>
+      <c r="AA11">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C12" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="J12" s="15">
+        <v>45943</v>
+      </c>
+      <c r="K12">
+        <v>8</v>
+      </c>
+      <c r="L12">
+        <v>12</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <v>4</v>
+      </c>
+      <c r="Q12">
+        <v>15</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>6</v>
+      </c>
+      <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>11</v>
+      </c>
+      <c r="V12">
+        <v>9</v>
+      </c>
+      <c r="W12">
+        <v>13</v>
+      </c>
+      <c r="X12">
+        <v>7</v>
+      </c>
+      <c r="Y12">
+        <v>3</v>
+      </c>
+      <c r="Z12">
+        <v>14</v>
+      </c>
+      <c r="AA12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C13" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D13" s="2">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="J13" s="15">
+        <v>45944</v>
+      </c>
+      <c r="K13">
+        <v>9</v>
+      </c>
+      <c r="L13">
+        <v>13</v>
+      </c>
+      <c r="M13">
+        <v>11</v>
+      </c>
+      <c r="N13">
+        <v>6</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
+      <c r="Q13">
+        <v>15</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>7</v>
+      </c>
+      <c r="T13">
+        <v>2</v>
+      </c>
+      <c r="U13">
+        <v>12</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>14</v>
+      </c>
+      <c r="X13">
+        <v>8</v>
+      </c>
+      <c r="Y13">
+        <v>4</v>
+      </c>
+      <c r="Z13">
+        <v>3</v>
+      </c>
+      <c r="AA13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C14" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D14" s="2">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J14" s="15">
+        <v>45945</v>
+      </c>
+      <c r="K14">
+        <v>8</v>
+      </c>
+      <c r="L14">
+        <v>11</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>6</v>
+      </c>
+      <c r="O14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>15</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>7</v>
+      </c>
+      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="U14">
+        <v>12</v>
+      </c>
+      <c r="V14">
+        <v>9</v>
+      </c>
+      <c r="W14">
+        <v>14</v>
+      </c>
+      <c r="X14">
+        <v>5</v>
+      </c>
+      <c r="Y14">
+        <v>4</v>
+      </c>
+      <c r="Z14">
+        <v>13</v>
+      </c>
+      <c r="AA14">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C15" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D15" s="2">
+        <v>12</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="J15" s="15">
+        <v>45946</v>
+      </c>
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15">
+        <v>11</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
+      <c r="Q15">
+        <v>14</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>7</v>
+      </c>
+      <c r="T15">
+        <v>2</v>
+      </c>
+      <c r="U15">
+        <v>12</v>
+      </c>
+      <c r="V15">
+        <v>9</v>
+      </c>
+      <c r="W15">
+        <v>13</v>
+      </c>
+      <c r="X15">
+        <v>5</v>
+      </c>
+      <c r="Y15">
+        <v>4</v>
+      </c>
+      <c r="AA15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C16" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D16" s="2">
+        <v>12</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="J16" s="15">
+        <v>45958</v>
+      </c>
+      <c r="M16">
+        <v>9</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="Q16">
+        <v>11</v>
+      </c>
+      <c r="S16">
+        <v>6</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>7</v>
+      </c>
+      <c r="V16">
+        <v>8</v>
+      </c>
+      <c r="W16">
+        <v>10</v>
+      </c>
+      <c r="Y16">
+        <v>3</v>
+      </c>
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C17" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D17" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G17" s="14"/>
+      <c r="J17" s="15">
+        <v>45959</v>
+      </c>
+      <c r="M17">
+        <v>9</v>
+      </c>
+      <c r="N17">
+        <v>5</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
+      </c>
+      <c r="Q17">
+        <v>11</v>
+      </c>
+      <c r="S17">
+        <v>6</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>7</v>
+      </c>
+      <c r="V17">
+        <v>8</v>
+      </c>
+      <c r="W17">
+        <v>10</v>
+      </c>
+      <c r="Y17">
+        <v>3</v>
+      </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
+      <c r="AA17">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C18" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D18" s="2">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="J18" s="15">
+        <v>45960</v>
+      </c>
+      <c r="M18">
+        <v>8</v>
+      </c>
+      <c r="N18">
+        <v>4</v>
+      </c>
+      <c r="O18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <v>10</v>
+      </c>
+      <c r="S18">
+        <v>5</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>6</v>
+      </c>
+      <c r="V18">
+        <v>7</v>
+      </c>
+      <c r="W18">
+        <v>9</v>
+      </c>
+      <c r="Z18">
+        <v>2</v>
+      </c>
+      <c r="AA18">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C19" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D19" s="2">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J19" s="15">
+        <v>45961</v>
+      </c>
+      <c r="M19">
+        <v>7</v>
+      </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
+      <c r="O19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>10</v>
+      </c>
+      <c r="S19">
+        <v>5</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>8</v>
+      </c>
+      <c r="V19">
+        <v>6</v>
+      </c>
+      <c r="W19">
+        <v>9</v>
+      </c>
+      <c r="Z19">
+        <v>2</v>
+      </c>
+      <c r="AA19">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C20" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D20" s="2">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J20" s="15">
+        <v>45964</v>
+      </c>
+      <c r="K20">
+        <v>9</v>
+      </c>
+      <c r="M20">
+        <v>7</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="Q20">
+        <v>11</v>
+      </c>
+      <c r="S20">
+        <v>5</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>8</v>
+      </c>
+      <c r="V20">
+        <v>6</v>
+      </c>
+      <c r="W20">
+        <v>10</v>
+      </c>
+      <c r="Z20">
+        <v>2</v>
+      </c>
+      <c r="AA20">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C21" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D21" s="2">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="K21">
+        <v>64</v>
+      </c>
+      <c r="L21">
+        <v>81</v>
+      </c>
+      <c r="M21">
+        <v>109</v>
+      </c>
+      <c r="N21">
+        <v>58</v>
+      </c>
+      <c r="O21">
+        <v>42</v>
+      </c>
+      <c r="P21">
+        <v>37</v>
+      </c>
+      <c r="Q21">
+        <v>156</v>
+      </c>
+      <c r="R21">
+        <v>7</v>
+      </c>
+      <c r="S21">
+        <v>70</v>
+      </c>
+      <c r="T21">
+        <v>19</v>
+      </c>
+      <c r="U21">
+        <v>114</v>
+      </c>
+      <c r="V21">
+        <v>97</v>
+      </c>
+      <c r="W21">
+        <v>142</v>
+      </c>
+      <c r="X21">
+        <v>44</v>
+      </c>
+      <c r="Y21">
+        <v>24</v>
+      </c>
+      <c r="Z21">
+        <v>55</v>
+      </c>
+      <c r="AA21">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C22" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C23" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D23" s="2">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C24" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D24" s="2">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C25" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D25" s="2">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C26" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D26" s="2">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C27" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D27" s="2">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C28" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D28" s="2">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C29" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D29" s="2">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C30" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D30" s="2">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C31" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D31" s="2">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.35">
+      <c r="C32" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C33" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C34" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D34" s="2">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C35" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D35" s="2">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C36" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D36" s="2">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C37" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D37" s="2">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C38" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D38" s="2">
+        <v>6</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C39" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D39" s="2">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C40" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D40" s="2">
+        <v>5</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C41" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C42" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D42" s="2">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C43" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C44" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C45" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C46" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C47" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D47" s="2">
+        <v>4</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C48" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C49" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C50" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D50" s="2">
+        <v>3</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C51" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C52" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D52" s="2">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C53" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D53" s="2">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C54" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D54" s="2">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C55" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D55" s="2">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C56" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D56" s="2">
+        <v>12</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C57" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D57" s="2">
+        <v>12</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C58" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D58" s="2">
+        <v>13</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C59" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D59" s="2">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C60" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D60" s="2">
+        <v>10</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C61" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D61" s="2">
+        <v>10</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C62" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D62" s="2">
+        <v>11</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="63" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C63" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D63" s="2">
+        <v>14</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C64" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D64" s="2">
+        <v>14</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C65" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D65" s="2">
+        <v>16</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C66" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D66" s="2">
+        <v>15</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C67" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D67" s="2">
+        <v>15</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C68" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D68" s="2">
+        <v>15</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C69" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D69" s="2">
+        <v>14</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C70" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D70" s="2">
+        <v>11</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C71" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D71" s="2">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C72" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C73" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C74" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C75" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D75" s="2">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C76" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D76" s="2">
+        <v>1</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C77" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D77" s="2">
+        <v>1</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C78" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D78" s="2">
+        <v>3</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C79" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D79" s="2">
+        <v>3</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C80" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D80" s="2">
+        <v>4</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C81" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D81" s="2">
+        <v>4</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C82" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D82" s="2">
+        <v>4</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C83" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D83" s="2">
+        <v>3</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C84" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D84" s="2">
+        <v>3</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C85" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D85" s="2">
+        <v>15</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C86" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D86" s="2">
+        <v>14</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C87" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D87" s="2">
+        <v>3</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C88" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D88" s="2">
+        <v>13</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C89" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C90" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="91" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C91" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C92" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D92" s="2">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C93" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D93" s="2">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C94" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D94" s="2">
+        <v>5</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="95" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C95" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D95" s="2">
+        <v>5</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C96" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D96" s="2">
+        <v>5</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C97" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D97" s="2">
+        <v>6</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="98" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C98" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D98" s="2">
+        <v>6</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="99" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C99" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D99" s="2">
+        <v>7</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="100" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C100" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D100" s="2">
+        <v>7</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="101" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C101" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D101" s="2">
+        <v>7</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="102" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C102" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D102" s="2">
+        <v>6</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="103" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C103" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D103" s="2">
+        <v>6</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="104" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C104" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D104" s="2">
+        <v>5</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="105" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C105" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D105" s="2">
+        <v>5</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="106" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C106" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C107" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D107" s="2">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="108" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C108" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D108" s="2">
+        <v>2</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C109" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D109" s="2">
+        <v>2</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="110" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C110" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D110" s="2">
+        <v>2</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="111" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C111" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D111" s="2">
+        <v>2</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="112" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C112" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D112" s="2">
+        <v>2</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="113" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C113" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D113" s="2">
+        <v>1</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="114" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C114" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D114" s="2">
+        <v>1</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="115" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C115" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="116" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C116" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D116" s="2">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="117" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C117" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D117" s="2">
+        <v>1</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="118" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C118" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D118" s="2">
+        <v>10</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="119" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C119" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D119" s="2">
+        <v>10</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="120" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C120" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D120" s="2">
+        <v>11</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="121" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C121" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D121" s="2">
+        <v>11</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C122" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D122" s="2">
+        <v>12</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="123" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C123" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D123" s="2">
+        <v>12</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="124" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C124" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D124" s="2">
+        <v>12</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="125" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C125" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D125" s="2">
+        <v>7</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="126" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C126" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D126" s="2">
+        <v>7</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="127" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C127" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D127" s="2">
+        <v>6</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="128" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C128" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D128" s="2">
+        <v>8</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C129" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D129" s="2">
+        <v>8</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C130" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D130" s="2">
+        <v>6</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C131" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D131" s="2">
+        <v>8</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C132" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D132" s="2">
+        <v>8</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C133" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D133" s="2">
+        <v>8</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C134" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D134" s="2">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C135" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D135" s="2">
+        <v>9</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C136" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D136" s="2">
+        <v>10</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C137" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D137" s="2">
+        <v>9</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="138" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C138" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D138" s="2">
+        <v>9</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="139" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C139" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D139" s="2">
+        <v>8</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="140" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C140" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D140" s="2">
+        <v>7</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C141" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D141" s="2">
+        <v>6</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C142" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D142" s="2">
+        <v>13</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C143" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D143" s="2">
+        <v>13</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C144" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D144" s="2">
+        <v>14</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C145" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D145" s="2">
+        <v>13</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C146" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D146" s="2">
+        <v>14</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C147" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D147" s="2">
+        <v>14</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C148" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D148" s="2">
+        <v>13</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="149" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C149" s="13">
+        <v>45958</v>
+      </c>
+      <c r="D149" s="2">
+        <v>10</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C150" s="13">
+        <v>45959</v>
+      </c>
+      <c r="D150" s="2">
+        <v>10</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="151" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C151" s="13">
+        <v>45960</v>
+      </c>
+      <c r="D151" s="2">
+        <v>9</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="152" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C152" s="13">
+        <v>45961</v>
+      </c>
+      <c r="D152" s="2">
+        <v>9</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="153" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C153" s="13">
+        <v>45964</v>
+      </c>
+      <c r="D153" s="2">
+        <v>10</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="154" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C154" s="13">
+        <v>45938</v>
+      </c>
+      <c r="D154" s="2">
+        <v>6</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="155" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C155" s="13">
+        <v>45939</v>
+      </c>
+      <c r="D155" s="2">
+        <v>6</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="156" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C156" s="13">
+        <v>45940</v>
+      </c>
+      <c r="D156" s="2">
+        <v>7</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="157" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C157" s="13">
+        <v>45943</v>
+      </c>
+      <c r="D157" s="2">
+        <v>7</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="158" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C158" s="13">
+        <v>45944</v>
+      </c>
+      <c r="D158" s="2">
+        <v>8</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="159" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C159" s="13">
+        <v>45945</v>
+      </c>
+      <c r="D159" s="2">
+        <v>5</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="160" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C160" s="13">
+        <v>45946</v>
+      </c>
+      <c r="D160" s="2">
+        <v>5</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="C4:E118" xr:uid="{C13F8141-B057-41CC-9C69-E52F2BA85FD5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C5:E160">
+      <sortCondition ref="E4:E118"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>